--- a/outputs/step3_disease_logistic/auc_delta_summary.xlsx
+++ b/outputs/step3_disease_logistic/auc_delta_summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="18">
   <si>
     <t>feature</t>
   </si>
@@ -22,7 +22,10 @@
     <t>cohort</t>
   </si>
   <si>
-    <t>aec_combo</t>
+    <t>aec_combo_clinic4_aec_best</t>
+  </si>
+  <si>
+    <t>aec_combo_clinic5_aec_best</t>
   </si>
   <si>
     <t>auc_clinic4</t>
@@ -31,13 +34,19 @@
     <t>auc_clinic4_aec_best</t>
   </si>
   <si>
-    <t>delta_auc_aec_best_minus_clinic4</t>
-  </si>
-  <si>
-    <t>delong_z</t>
-  </si>
-  <si>
-    <t>delong_p_value</t>
+    <t>auc_clinic5_aec_best</t>
+  </si>
+  <si>
+    <t>delta_auc_clinic4_aec_best_minus_clinic4</t>
+  </si>
+  <si>
+    <t>delong_p_clinic4_aec_best</t>
+  </si>
+  <si>
+    <t>delta_auc_clinic5_aec_best_minus_clinic4</t>
+  </si>
+  <si>
+    <t>delong_p_clinic5_aec_best</t>
   </si>
   <si>
     <t>HTN</t>
@@ -56,6 +65,9 @@
   </si>
   <si>
     <t>FPCA</t>
+  </si>
+  <si>
+    <t>전체결합: SD·Skew·상하위비율·FPCA</t>
   </si>
 </sst>
 </file>
@@ -413,10 +425,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -441,161 +453,224 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2">
+        <v>0.8065</v>
+      </c>
+      <c r="F2">
+        <v>0.8176</v>
+      </c>
+      <c r="G2">
+        <v>0.8179</v>
+      </c>
+      <c r="H2">
+        <v>0.0112</v>
+      </c>
+      <c r="I2">
+        <v>0.0267</v>
+      </c>
+      <c r="J2">
+        <v>0.0115</v>
+      </c>
+      <c r="K2">
+        <v>0.0295</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3">
+        <v>0.7135</v>
+      </c>
+      <c r="F3">
+        <v>0.731</v>
+      </c>
+      <c r="G3">
+        <v>0.7367</v>
+      </c>
+      <c r="H3">
+        <v>0.0175</v>
+      </c>
+      <c r="I3">
+        <v>0.0035</v>
+      </c>
+      <c r="J3">
+        <v>0.0232</v>
+      </c>
+      <c r="K3">
+        <v>0.0004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4">
+        <v>0.7296</v>
+      </c>
+      <c r="F4">
+        <v>0.7509</v>
+      </c>
+      <c r="G4">
+        <v>0.7497</v>
+      </c>
+      <c r="H4">
+        <v>0.0214</v>
+      </c>
+      <c r="I4">
+        <v>0.0282</v>
+      </c>
+      <c r="J4">
+        <v>0.0202</v>
+      </c>
+      <c r="K4">
+        <v>0.0411</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5">
+        <v>0.6625</v>
+      </c>
+      <c r="F5">
+        <v>0.7014</v>
+      </c>
+      <c r="G5">
+        <v>0.7032</v>
+      </c>
+      <c r="H5">
+        <v>0.0389</v>
+      </c>
+      <c r="I5">
+        <v>0.0001</v>
+      </c>
+      <c r="J5">
+        <v>0.0407</v>
+      </c>
+      <c r="K5">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="D2">
-        <v>0.8082</v>
-      </c>
-      <c r="E2">
-        <v>0.8177</v>
-      </c>
-      <c r="F2">
-        <v>0.0094</v>
-      </c>
-      <c r="G2">
-        <v>1.8858</v>
-      </c>
-      <c r="H2">
-        <v>0.0593</v>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>0.7935</v>
+      </c>
+      <c r="F6">
+        <v>0.8129</v>
+      </c>
+      <c r="G6">
+        <v>0.8212</v>
+      </c>
+      <c r="H6">
+        <v>0.0194</v>
+      </c>
+      <c r="I6">
+        <v>0.1661</v>
+      </c>
+      <c r="J6">
+        <v>0.0277</v>
+      </c>
+      <c r="K6">
+        <v>0.09030000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="D3">
-        <v>0.715</v>
-      </c>
-      <c r="E3">
-        <v>0.7313</v>
-      </c>
-      <c r="F3">
-        <v>0.0164</v>
-      </c>
-      <c r="G3">
-        <v>2.7851</v>
-      </c>
-      <c r="H3">
-        <v>0.0054</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4">
-        <v>0.7275</v>
-      </c>
-      <c r="E4">
-        <v>0.752</v>
-      </c>
-      <c r="F4">
-        <v>0.0246</v>
-      </c>
-      <c r="G4">
-        <v>2.6881</v>
-      </c>
-      <c r="H4">
-        <v>0.0072</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5">
-        <v>0.6625</v>
-      </c>
-      <c r="E5">
-        <v>0.6992</v>
-      </c>
-      <c r="F5">
-        <v>0.0367</v>
-      </c>
-      <c r="G5">
-        <v>3.7472</v>
-      </c>
-      <c r="H5">
-        <v>0.0002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>0.7903</v>
-      </c>
-      <c r="E6">
-        <v>0.8066</v>
-      </c>
-      <c r="F6">
-        <v>0.0163</v>
-      </c>
-      <c r="G6">
-        <v>1.3393</v>
-      </c>
-      <c r="H6">
-        <v>0.1805</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7">
-        <v>0.6215000000000001</v>
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
       </c>
       <c r="E7">
-        <v>0.6435999999999999</v>
+        <v>0.6214</v>
       </c>
       <c r="F7">
-        <v>0.0221</v>
+        <v>0.6414</v>
       </c>
       <c r="G7">
-        <v>2.3307</v>
+        <v>0.6351</v>
       </c>
       <c r="H7">
-        <v>0.0198</v>
+        <v>0.02</v>
+      </c>
+      <c r="I7">
+        <v>0.0342</v>
+      </c>
+      <c r="J7">
+        <v>0.0138</v>
+      </c>
+      <c r="K7">
+        <v>0.2343</v>
       </c>
     </row>
   </sheetData>
